--- a/public/exports-60-250/29189978.xlsx
+++ b/public/exports-60-250/29189978.xlsx
@@ -5314,7 +5314,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000943</t>
+          <t xml:space="preserve">310000942</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411362</t>
+          <t xml:space="preserve">311411363</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M110" t="inlineStr">
